--- a/data/excel-and-bi-tools--sales-explorer.xlsx
+++ b/data/excel-and-bi-tools--sales-explorer.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Explore" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8442,4 +8443,63 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A teaching dataset written for the book. It holds 150 orders placed in 2024 with a made-up retailer, laid out for exploring in Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>The Dashboard, Calcs, Descriptive Stats, Cross-Tab and Regression sheets are live formulas on the Data sheet, so changing a value there updates every summary and chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Start with How to Explore, which suggests a PivotTable, a new chart and a Goal Seek to try.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>The Codebook sheet describes the ten columns. Revenue is in dollars after discount, so on 51 of the 150 orders it is 10 or 20 percent below units times unit price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Unlike most of the book's datasets, this one has no planted faults, so it can go straight into a PivotTable.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>